--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="2"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="65">
   <si>
     <t>시트구분</t>
   </si>
@@ -867,7 +867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -892,1473 +892,1467 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C4">
-        <v>72</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C5">
-        <v>197</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>73</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8">
-        <v>140</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>88</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C16">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18">
-        <v>46</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C19">
-        <v>75</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C23">
-        <v>61</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C25">
-        <v>55</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C28">
-        <v>650</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C29">
-        <v>670</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C30">
-        <v>821</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31">
-        <v>919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
         <v>29</v>
       </c>
       <c r="C32">
-        <v>918</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33">
-        <v>1052</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C34">
-        <v>502</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C35">
-        <v>375</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C36">
-        <v>560</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C37">
-        <v>565</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C38">
-        <v>435</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>268</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C41">
-        <v>420</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42">
-        <v>725</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C43">
-        <v>190</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>474</v>
+        <v>775</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C45">
-        <v>50</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C46">
-        <v>400</v>
+        <v>455</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C48">
-        <v>485</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>40</v>
       </c>
       <c r="C49">
-        <v>215</v>
+        <v>634</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>37</v>
       </c>
       <c r="C50">
-        <v>100</v>
+        <v>954</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>772</v>
+        <v>581</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C52">
-        <v>236</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>869</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C54">
-        <v>35</v>
+        <v>623</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C55">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C56">
-        <v>50</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C57">
-        <v>285</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C58">
-        <v>500</v>
+        <v>725</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C59">
-        <v>61</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" t="s">
-        <v>34</v>
+        <v>59</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46082</v>
       </c>
       <c r="C60">
-        <v>434</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61">
         <v>10</v>
-      </c>
-      <c r="B61" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>46327</v>
+        <v>45901</v>
       </c>
       <c r="C62">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" t="s">
-        <v>40</v>
+        <v>61</v>
+      </c>
+      <c r="B63" s="3">
+        <v>45962</v>
       </c>
       <c r="C63">
-        <v>762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C64">
-        <v>974</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C65">
-        <v>921</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C66">
-        <v>810</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" t="s">
-        <v>31</v>
+        <v>60</v>
+      </c>
+      <c r="B67" s="3">
+        <v>45748</v>
       </c>
       <c r="C67">
-        <v>495</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" t="s">
-        <v>41</v>
+        <v>60</v>
+      </c>
+      <c r="B68" s="3">
+        <v>45778</v>
       </c>
       <c r="C68">
-        <v>540</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="B69" s="3">
+        <v>45809</v>
       </c>
       <c r="C69">
-        <v>130</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" t="s">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="3">
+        <v>45839</v>
       </c>
       <c r="C70">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" t="s">
-        <v>35</v>
+        <v>60</v>
+      </c>
+      <c r="B71" s="3">
+        <v>45870</v>
       </c>
       <c r="C71">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" t="s">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="B72" s="3">
+        <v>45931</v>
       </c>
       <c r="C72">
-        <v>675</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" t="s">
-        <v>33</v>
+        <v>60</v>
+      </c>
+      <c r="B73" s="3">
+        <v>45962</v>
       </c>
       <c r="C73">
-        <v>300</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C75">
-        <v>42</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C76">
-        <v>45</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C77">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C78">
-        <v>474</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C79">
-        <v>38</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
       </c>
       <c r="C80">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B81" t="s">
         <v>34</v>
       </c>
       <c r="C81">
-        <v>200</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B82" t="s">
         <v>35</v>
       </c>
       <c r="C82">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B83" t="s">
         <v>36</v>
       </c>
       <c r="C83">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B84" t="s">
         <v>33</v>
       </c>
       <c r="C84">
-        <v>150</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="B85" s="3">
+        <v>46327</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B86" t="s">
         <v>37</v>
       </c>
       <c r="C86">
-        <v>16</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B87" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C87">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C88">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C90">
-        <v>125</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C91">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C92">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C93">
-        <v>185</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B94" t="s">
-        <v>36</v>
+        <v>5</v>
+      </c>
+      <c r="B94" s="3">
+        <v>46327</v>
       </c>
       <c r="C94">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C95">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C96">
-        <v>240</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C97">
-        <v>366</v>
+        <v>85</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C98">
-        <v>269</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C99">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C100">
-        <v>280</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B101" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C101">
-        <v>229</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102">
         <v>19</v>
-      </c>
-      <c r="B102" t="s">
-        <v>32</v>
-      </c>
-      <c r="C102">
-        <v>775</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C103">
-        <v>489</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C104">
-        <v>455</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C105">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C106">
-        <v>100</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C107">
-        <v>634</v>
+        <v>185</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C108">
-        <v>954</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C109">
-        <v>581</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C110">
-        <v>1048</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C111">
-        <v>869</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C112">
-        <v>623</v>
+        <v>161</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C113">
-        <v>269</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C114">
-        <v>282</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C115">
-        <v>420</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C116">
-        <v>725</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
         <v>33</v>
       </c>
       <c r="C117">
-        <v>600</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>57</v>
-      </c>
-      <c r="B118" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="B118" s="3">
+        <v>46327</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C119">
-        <v>196</v>
+        <v>650</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C120">
-        <v>185</v>
+        <v>670</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C121">
-        <v>153</v>
+        <v>821</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C122">
-        <v>266</v>
+        <v>919</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>56</v>
+        <v>918</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C124">
-        <v>68</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B125" t="s">
         <v>31</v>
       </c>
       <c r="C125">
-        <v>161</v>
+        <v>502</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B126" t="s">
         <v>41</v>
       </c>
       <c r="C126">
-        <v>165</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C127">
-        <v>72</v>
+        <v>560</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>565</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C129">
-        <v>155</v>
+        <v>625</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B130" t="s">
         <v>33</v>
       </c>
       <c r="C130">
-        <v>50</v>
+        <v>263</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>24</v>
-      </c>
-      <c r="B131" t="s">
-        <v>32</v>
+        <v>7</v>
+      </c>
+      <c r="B131" s="3">
+        <v>46327</v>
       </c>
       <c r="C131">
-        <v>37</v>
+        <v>263</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C132">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C133">
-        <v>10</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>22</v>
-      </c>
-      <c r="B134" s="3">
-        <v>46327</v>
+        <v>8</v>
+      </c>
+      <c r="B134" t="s">
+        <v>32</v>
       </c>
       <c r="C134">
-        <v>70</v>
+        <v>725</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C135">
-        <v>60</v>
+        <v>190</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>4</v>
-      </c>
-      <c r="B136" s="3">
-        <v>46327</v>
+        <v>8</v>
+      </c>
+      <c r="B136" t="s">
+        <v>35</v>
       </c>
       <c r="C136">
-        <v>20</v>
+        <v>474</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>5</v>
-      </c>
-      <c r="B137" s="3">
-        <v>46327</v>
+        <v>8</v>
+      </c>
+      <c r="B137" t="s">
+        <v>36</v>
       </c>
       <c r="C137">
         <v>50</v>
@@ -2366,13 +2360,13 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>7</v>
-      </c>
-      <c r="B138" s="3">
-        <v>46327</v>
+        <v>8</v>
+      </c>
+      <c r="B138" t="s">
+        <v>33</v>
       </c>
       <c r="C138">
-        <v>263</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
@@ -2390,173 +2384,193 @@
       <c r="A140" t="s">
         <v>9</v>
       </c>
-      <c r="B140" s="3">
-        <v>46327</v>
+      <c r="B140" t="s">
+        <v>38</v>
       </c>
       <c r="C140">
-        <v>120</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>59</v>
-      </c>
-      <c r="B141" s="3">
-        <v>46082</v>
+        <v>9</v>
+      </c>
+      <c r="B141" t="s">
+        <v>39</v>
       </c>
       <c r="C141">
-        <v>4</v>
+        <v>485</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>60</v>
-      </c>
-      <c r="B142" s="3">
-        <v>45748</v>
+        <v>9</v>
+      </c>
+      <c r="B142" t="s">
+        <v>40</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>215</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="B143" t="s">
+        <v>37</v>
+      </c>
+      <c r="C143">
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C144">
-        <v>10</v>
+        <v>772</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>61</v>
-      </c>
-      <c r="B145" s="3">
-        <v>45901</v>
+        <v>9</v>
+      </c>
+      <c r="B145" t="s">
+        <v>31</v>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>61</v>
-      </c>
-      <c r="B146" s="3">
-        <v>45962</v>
+        <v>9</v>
+      </c>
+      <c r="B146" t="s">
+        <v>41</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C147">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C148">
-        <v>6</v>
+        <v>350</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C149">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>60</v>
-      </c>
-      <c r="B150" s="3">
-        <v>45778</v>
+        <v>9</v>
+      </c>
+      <c r="B150" t="s">
+        <v>33</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B151" s="3">
-        <v>45809</v>
+        <v>46327</v>
       </c>
       <c r="C151">
-        <v>3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>60</v>
-      </c>
-      <c r="B152" s="3">
-        <v>45839</v>
+        <v>10</v>
+      </c>
+      <c r="B152" t="s">
+        <v>41</v>
       </c>
       <c r="C152">
-        <v>3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>60</v>
-      </c>
-      <c r="B153" s="3">
-        <v>45870</v>
+        <v>10</v>
+      </c>
+      <c r="B153" t="s">
+        <v>32</v>
       </c>
       <c r="C153">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>60</v>
-      </c>
-      <c r="B154" s="3">
-        <v>45931</v>
+        <v>10</v>
+      </c>
+      <c r="B154" t="s">
+        <v>34</v>
       </c>
       <c r="C154">
-        <v>3</v>
+        <v>434</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>60</v>
-      </c>
-      <c r="B155" s="3">
-        <v>45962</v>
+        <v>10</v>
+      </c>
+      <c r="B155" t="s">
+        <v>36</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>10</v>
+      </c>
+      <c r="B156" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C156">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:C156">
+    <sortCondition ref="A4:A156"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\업무\Claude\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH-3348\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D8773F-EEF7-4D4D-B5C0-C7EDB813CD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -21,24 +22,11 @@
     <sheet name="SAP-600 MB" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="65">
   <si>
     <t>시트구분</t>
   </si>
@@ -246,7 +234,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -599,11 +587,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -619,7 +607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -627,7 +615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -635,7 +623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -643,7 +631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -651,7 +639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -659,7 +647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -667,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -675,7 +663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -683,7 +671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -691,7 +679,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -699,7 +687,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -707,7 +695,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -715,7 +703,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -723,7 +711,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -731,7 +719,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -739,7 +727,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -747,7 +735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -755,7 +743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -763,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -771,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -779,7 +767,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -787,7 +775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -795,7 +783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -803,7 +791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -811,7 +799,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -819,7 +807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -827,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -835,7 +823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>2</v>
       </c>
@@ -843,7 +831,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -851,7 +839,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -866,20 +854,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C156"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C161"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.19921875" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.25" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -890,7 +878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -901,7 +889,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -912,7 +900,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -923,7 +911,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -934,7 +922,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -945,7 +933,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -956,7 +944,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -967,7 +955,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -978,7 +966,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -989,7 +977,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1000,7 +988,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1011,7 +999,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1022,7 +1010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1033,7 +1021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1044,7 +1032,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1055,7 +1043,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1066,7 +1054,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1077,7 +1065,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1088,7 +1076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1099,7 +1087,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1110,7 +1098,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -1121,7 +1109,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1132,7 +1120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1143,7 +1131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -1154,7 +1142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -1165,7 +1153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1176,7 +1164,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1187,7 +1175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1198,7 +1186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1209,7 +1197,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -1220,7 +1208,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1231,7 +1219,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -1242,7 +1230,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -1253,7 +1241,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -1264,7 +1252,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -1275,7 +1263,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -1286,7 +1274,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1297,7 +1285,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1308,7 +1296,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -1319,7 +1307,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -1330,7 +1318,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -1341,7 +1329,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -1352,7 +1340,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1363,7 +1351,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -1374,7 +1362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -1385,7 +1373,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -1396,7 +1384,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -1407,7 +1395,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -1418,7 +1406,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -1429,7 +1417,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -1440,7 +1428,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -1451,7 +1439,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -1462,7 +1450,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -1473,7 +1461,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -1484,7 +1472,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -1495,7 +1483,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -1506,7 +1494,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1517,7 +1505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1528,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1539,7 +1527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1550,7 +1538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -1561,7 +1549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -1572,7 +1560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -1583,7 +1571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -1594,7 +1582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>60</v>
       </c>
@@ -1605,7 +1593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>60</v>
       </c>
@@ -1616,7 +1604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>60</v>
       </c>
@@ -1627,7 +1615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>60</v>
       </c>
@@ -1638,7 +1626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>60</v>
       </c>
@@ -1649,7 +1637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>60</v>
       </c>
@@ -1660,12 +1648,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -1676,7 +1664,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -1687,7 +1675,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -1698,7 +1686,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1697,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -1717,858 +1705,913 @@
         <v>33</v>
       </c>
       <c r="C79">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" t="s">
-        <v>32</v>
+        <v>3</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46357</v>
       </c>
       <c r="C80">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C81">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C82">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C83">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C84">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>4</v>
       </c>
-      <c r="B85" s="3">
-        <v>46327</v>
+      <c r="B85" t="s">
+        <v>33</v>
       </c>
       <c r="C85">
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>5</v>
-      </c>
-      <c r="B86" t="s">
-        <v>37</v>
+        <v>4</v>
+      </c>
+      <c r="B86" s="3">
+        <v>46327</v>
       </c>
       <c r="C86">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>5</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C87">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C88">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C90">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C91">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C92">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C93">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>5</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="3">
         <v>46327</v>
       </c>
-      <c r="C94">
+      <c r="C95">
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>6</v>
-      </c>
-      <c r="B95" t="s">
-        <v>31</v>
-      </c>
-      <c r="C95">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C97">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C98">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" s="3">
+        <v>46357</v>
+      </c>
+      <c r="C101">
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" t="s">
-        <v>32</v>
-      </c>
-      <c r="C101">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C102">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C103">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>24</v>
       </c>
       <c r="B105" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106" t="s">
         <v>33</v>
       </c>
-      <c r="C105">
+      <c r="C106">
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" t="s">
-        <v>42</v>
-      </c>
-      <c r="C106">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C107">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C108">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C109">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C110">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C111">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C112">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C113">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C114">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C115">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C116">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C117">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>22</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" t="s">
+        <v>33</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="3">
         <v>46327</v>
       </c>
-      <c r="C118">
+      <c r="C119">
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>7</v>
-      </c>
-      <c r="B119" t="s">
-        <v>38</v>
-      </c>
-      <c r="C119">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>7</v>
-      </c>
-      <c r="B120" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="B120" s="3">
+        <v>46357</v>
       </c>
       <c r="C120">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C121">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C122">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C123">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C124">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C126">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C127">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C128">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C129">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C130">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>7</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>33</v>
+      </c>
+      <c r="C132">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>7</v>
+      </c>
+      <c r="B133" s="3">
         <v>46327</v>
       </c>
-      <c r="C131">
+      <c r="C133">
         <v>263</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A132" t="s">
-        <v>8</v>
-      </c>
-      <c r="B132" t="s">
-        <v>31</v>
-      </c>
-      <c r="C132">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A133" t="s">
-        <v>8</v>
-      </c>
-      <c r="B133" t="s">
-        <v>41</v>
-      </c>
-      <c r="C133">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>8</v>
-      </c>
-      <c r="B134" t="s">
-        <v>32</v>
+        <v>7</v>
+      </c>
+      <c r="B134" s="3">
+        <v>46357</v>
       </c>
       <c r="C134">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C135">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C136">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C137">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C138">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>8</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" t="s">
+        <v>35</v>
+      </c>
+      <c r="C139">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" t="s">
+        <v>36</v>
+      </c>
+      <c r="C140">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>33</v>
+      </c>
+      <c r="C141">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" s="3">
         <v>46327</v>
       </c>
-      <c r="C139">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="B140" t="s">
-        <v>38</v>
-      </c>
-      <c r="C140">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="B141" t="s">
-        <v>39</v>
-      </c>
-      <c r="C141">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="B142" t="s">
-        <v>40</v>
-      </c>
       <c r="C142">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="B143" s="3">
+        <v>46357</v>
       </c>
       <c r="C143">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C144">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C145">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C146">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C147">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C148">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C149">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C150">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>9</v>
       </c>
-      <c r="B151" s="3">
+      <c r="B151" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
+        <v>35</v>
+      </c>
+      <c r="C152">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
+        <v>33</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" s="3">
         <v>46327</v>
       </c>
-      <c r="C151">
+      <c r="C155">
         <v>120</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="3">
+        <v>46357</v>
+      </c>
+      <c r="C156">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>10</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B157" t="s">
         <v>41</v>
       </c>
-      <c r="C152">
+      <c r="C157">
         <v>500</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>10</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B158" t="s">
         <v>32</v>
       </c>
-      <c r="C153">
+      <c r="C158">
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>10</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B159" t="s">
         <v>34</v>
       </c>
-      <c r="C154">
+      <c r="C159">
         <v>434</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>10</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B160" t="s">
         <v>36</v>
       </c>
-      <c r="C155">
+      <c r="C160">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>10</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B161" s="3">
         <v>46327</v>
       </c>
-      <c r="C156">
+      <c r="C161">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A4:C156">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:C156">
     <sortCondition ref="A4:A156"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2577,20 +2620,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.8984375" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.875" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -2604,7 +2647,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2618,7 +2661,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2675,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2646,7 +2689,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2660,7 +2703,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2674,7 +2717,7 @@
         <v>177.6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2688,7 +2731,7 @@
         <v>182.6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2702,7 +2745,7 @@
         <v>206.9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2716,7 +2759,7 @@
         <v>89.9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2730,7 +2773,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2744,7 +2787,7 @@
         <v>106.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2758,7 +2801,7 @@
         <v>104.8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -2772,7 +2815,7 @@
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2786,7 +2829,7 @@
         <v>84.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2800,7 +2843,7 @@
         <v>93.9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2814,7 +2857,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2828,7 +2871,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2842,7 +2885,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -2856,7 +2899,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -2870,7 +2913,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2884,7 +2927,7 @@
         <v>92.4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -2898,7 +2941,7 @@
         <v>116.4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -2912,7 +2955,7 @@
         <v>114.4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2926,7 +2969,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2940,7 +2983,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -2954,7 +2997,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2968,7 +3011,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2982,7 +3025,7 @@
         <v>77.2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2996,7 +3039,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -3010,7 +3053,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -3024,7 +3067,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3038,7 +3081,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -3052,7 +3095,7 @@
         <v>111.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3066,7 +3109,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -3080,7 +3123,7 @@
         <v>117.8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3094,7 +3137,7 @@
         <v>117.4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -3108,7 +3151,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -3122,7 +3165,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -3136,7 +3179,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -3144,7 +3187,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -3152,7 +3195,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3160,7 +3203,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3174,7 +3217,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -3182,7 +3225,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3190,7 +3233,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3198,7 +3241,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -3212,7 +3255,7 @@
         <v>162.30000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -3226,7 +3269,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -3240,7 +3283,7 @@
         <v>164.1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3255,20 +3298,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3282,7 +3325,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3296,7 +3339,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3310,7 +3353,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3324,7 +3367,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3338,7 +3381,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3352,7 +3395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3366,7 +3409,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3380,7 +3423,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3394,7 +3437,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3408,7 +3451,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3422,7 +3465,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3436,7 +3479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3450,7 +3493,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -3464,7 +3507,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3478,7 +3521,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -3492,7 +3535,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -3506,7 +3549,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -3520,7 +3563,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -3534,7 +3577,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -3548,7 +3591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -3562,7 +3605,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -3583,19 +3626,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3609,7 +3652,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3623,7 +3666,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3637,7 +3680,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3651,7 +3694,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3665,7 +3708,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3679,7 +3722,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3693,7 +3736,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -3707,7 +3750,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3721,7 +3764,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -3735,7 +3778,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3749,7 +3792,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -3761,6 +3804,20 @@
       </c>
       <c r="D14">
         <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C15">
+        <v>3000</v>
+      </c>
+      <c r="D15">
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -3770,20 +3827,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.8984375" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.875" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3797,7 +3854,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3811,7 +3868,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3825,7 +3882,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3839,7 +3896,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3853,7 +3910,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3867,7 +3924,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3888,20 +3945,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.19921875" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.25" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3915,7 +3972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3929,7 +3986,7 @@
         <v>149.4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3943,10 +4000,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH-3348\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\업무\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D8773F-EEF7-4D4D-B5C0-C7EDB813CD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="67">
   <si>
     <t>시트구분</t>
   </si>
@@ -228,13 +227,21 @@
   </si>
   <si>
     <t>ASTRA i5 12th (44B)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8GB(Crucial)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8GB(Crucial)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -281,11 +288,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -587,11 +595,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="64.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -607,7 +618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -615,7 +626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -623,7 +634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -631,7 +642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -639,7 +650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -647,7 +658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -655,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -663,7 +674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -671,7 +682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -679,7 +690,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -687,7 +698,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -695,7 +706,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -703,7 +714,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -711,7 +722,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -719,7 +730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -727,7 +738,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -735,7 +746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -743,7 +754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -751,7 +762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -759,7 +770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -767,7 +778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -775,7 +786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -783,7 +794,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -791,7 +802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -799,7 +810,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -807,7 +818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -815,7 +826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -823,7 +834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>2</v>
       </c>
@@ -831,7 +842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -839,12 +850,20 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>2</v>
       </c>
       <c r="B32" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -854,20 +873,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C161"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="29.25" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.19921875" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -878,7 +897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -889,7 +908,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -900,7 +919,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -911,7 +930,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -922,7 +941,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -933,7 +952,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -944,7 +963,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -955,7 +974,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -966,7 +985,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -977,7 +996,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -988,7 +1007,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -999,7 +1018,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1010,7 +1029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1021,7 +1040,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1032,7 +1051,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1043,7 +1062,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1054,7 +1073,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1065,7 +1084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1076,7 +1095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1087,7 +1106,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1098,7 +1117,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -1109,7 +1128,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1120,7 +1139,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1131,7 +1150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -1142,7 +1161,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -1153,7 +1172,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1164,7 +1183,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1175,7 +1194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1186,7 +1205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1197,7 +1216,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -1208,7 +1227,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1219,7 +1238,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -1230,7 +1249,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -1241,7 +1260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -1252,7 +1271,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -1263,7 +1282,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -1274,7 +1293,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1285,7 +1304,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1296,7 +1315,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -1307,7 +1326,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -1318,7 +1337,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -1329,7 +1348,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -1340,7 +1359,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1351,7 +1370,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -1362,7 +1381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -1373,7 +1392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -1384,7 +1403,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -1395,7 +1414,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -1406,7 +1425,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -1417,7 +1436,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -1428,7 +1447,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -1439,7 +1458,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -1450,7 +1469,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -1461,7 +1480,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -1472,7 +1491,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -1483,7 +1502,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -1494,7 +1513,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1505,7 +1524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1516,7 +1535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1527,7 +1546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1538,7 +1557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -1549,7 +1568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -1560,7 +1579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -1571,7 +1590,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>60</v>
       </c>
@@ -1593,7 +1612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>60</v>
       </c>
@@ -1604,7 +1623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>60</v>
       </c>
@@ -1615,7 +1634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>60</v>
       </c>
@@ -1626,7 +1645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>60</v>
       </c>
@@ -1637,7 +1656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>60</v>
       </c>
@@ -1648,12 +1667,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1683,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1694,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1705,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1716,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -1730,7 +1749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -1741,7 +1760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -1752,7 +1771,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -1763,7 +1782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -1774,7 +1793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -1785,7 +1804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -1796,7 +1815,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -1818,7 +1837,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -1829,7 +1848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -1840,7 +1859,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -1851,7 +1870,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -1862,7 +1881,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -1873,7 +1892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -1884,7 +1903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>6</v>
       </c>
@@ -1895,7 +1914,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -1906,7 +1925,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -1917,7 +1936,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -1928,7 +1947,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -1939,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -1950,7 +1969,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>24</v>
       </c>
@@ -1961,7 +1980,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>24</v>
       </c>
@@ -1972,7 +1991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>24</v>
       </c>
@@ -1983,7 +2002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>24</v>
       </c>
@@ -1994,7 +2013,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>24</v>
       </c>
@@ -2005,7 +2024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -2016,7 +2035,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -2027,7 +2046,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -2038,7 +2057,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -2049,7 +2068,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -2060,7 +2079,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -2071,7 +2090,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>22</v>
       </c>
@@ -2082,7 +2101,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>22</v>
       </c>
@@ -2093,7 +2112,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>22</v>
       </c>
@@ -2104,7 +2123,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>22</v>
       </c>
@@ -2115,7 +2134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>22</v>
       </c>
@@ -2126,7 +2145,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -2137,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>22</v>
       </c>
@@ -2148,7 +2167,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>22</v>
       </c>
@@ -2159,7 +2178,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -2170,7 +2189,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -2181,7 +2200,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -2192,7 +2211,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -2203,7 +2222,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -2214,7 +2233,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -2225,7 +2244,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -2236,7 +2255,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -2247,7 +2266,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -2258,7 +2277,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -2269,7 +2288,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>7</v>
       </c>
@@ -2280,7 +2299,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -2291,7 +2310,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>7</v>
       </c>
@@ -2302,7 +2321,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -2313,7 +2332,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -2324,7 +2343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2354,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -2346,7 +2365,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -2357,7 +2376,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -2368,7 +2387,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2398,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -2390,7 +2409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2401,7 +2420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -2412,7 +2431,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -2423,7 +2442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -2434,7 +2453,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -2445,7 +2464,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -2456,7 +2475,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -2467,7 +2486,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>9</v>
       </c>
@@ -2478,7 +2497,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>9</v>
       </c>
@@ -2489,7 +2508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>9</v>
       </c>
@@ -2500,7 +2519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -2511,7 +2530,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -2522,7 +2541,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -2533,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -2544,7 +2563,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -2555,7 +2574,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -2566,7 +2585,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -2577,7 +2596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -2588,7 +2607,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -2599,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>10</v>
       </c>
@@ -2611,7 +2630,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:C156">
+  <sortState ref="A4:C156">
     <sortCondition ref="A4:A156"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2620,20 +2639,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30.875" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.8984375" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -2647,7 +2666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2661,7 +2680,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2675,7 +2694,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2689,7 +2708,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2703,7 +2722,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2717,7 +2736,7 @@
         <v>177.6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2731,7 +2750,7 @@
         <v>182.6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2745,7 +2764,7 @@
         <v>206.9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2759,7 +2778,7 @@
         <v>89.9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2773,7 +2792,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2787,7 +2806,7 @@
         <v>106.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2801,7 +2820,7 @@
         <v>104.8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -2815,7 +2834,7 @@
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2829,7 +2848,7 @@
         <v>84.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2843,7 +2862,7 @@
         <v>93.9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2857,7 +2876,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2871,7 +2890,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2885,7 +2904,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -2899,7 +2918,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -2913,7 +2932,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2927,7 +2946,7 @@
         <v>92.4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -2941,7 +2960,7 @@
         <v>116.4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -2955,7 +2974,7 @@
         <v>114.4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +2988,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2983,7 +3002,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -2997,7 +3016,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -3011,7 +3030,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3025,7 +3044,7 @@
         <v>77.2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3039,7 +3058,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -3053,7 +3072,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -3067,7 +3086,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3081,7 +3100,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -3095,7 +3114,7 @@
         <v>111.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3109,7 +3128,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -3123,7 +3142,7 @@
         <v>117.8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3137,7 +3156,7 @@
         <v>117.4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -3151,7 +3170,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -3165,7 +3184,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -3179,7 +3198,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -3187,7 +3206,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -3195,7 +3214,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3203,7 +3222,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3217,7 +3236,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -3225,7 +3244,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3233,7 +3252,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3241,7 +3260,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -3255,7 +3274,7 @@
         <v>162.30000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -3269,7 +3288,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -3283,7 +3302,7 @@
         <v>164.1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3298,20 +3317,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3325,7 +3344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3339,7 +3358,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3353,7 +3372,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3367,7 +3386,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3381,7 +3400,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3395,7 +3414,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3409,7 +3428,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3423,7 +3442,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3437,7 +3456,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3451,7 +3470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3465,7 +3484,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3479,7 +3498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3493,7 +3512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -3507,7 +3526,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3521,7 +3540,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -3535,7 +3554,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -3549,7 +3568,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -3563,7 +3582,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -3577,7 +3596,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -3591,7 +3610,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -3605,7 +3624,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -3626,19 +3645,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3652,7 +3671,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3666,7 +3685,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3680,7 +3699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3694,7 +3713,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3708,7 +3727,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3722,7 +3741,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3736,7 +3755,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -3750,7 +3769,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3764,7 +3783,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -3778,7 +3797,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3792,7 +3811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -3806,7 +3825,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -3817,6 +3836,20 @@
         <v>3000</v>
       </c>
       <c r="D15">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C16">
+        <v>3000</v>
+      </c>
+      <c r="D16">
         <v>44.5</v>
       </c>
     </row>
@@ -3827,20 +3860,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="59.875" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.8984375" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3854,7 +3887,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3868,7 +3901,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3882,7 +3915,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3896,7 +3929,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3910,7 +3943,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3924,7 +3957,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3945,20 +3978,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40.25" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.19921875" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3972,7 +4005,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3986,7 +4019,7 @@
         <v>149.4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -4000,10 +4033,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B7" s="2"/>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="67">
   <si>
     <t>시트구분</t>
   </si>
@@ -874,7 +874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -1724,7 +1724,7 @@
         <v>33</v>
       </c>
       <c r="C79">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
@@ -1801,18 +1801,18 @@
         <v>46327</v>
       </c>
       <c r="C86">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87" t="s">
-        <v>37</v>
+        <v>4</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46357</v>
       </c>
       <c r="C87">
-        <v>88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
@@ -1820,10 +1820,10 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
@@ -1831,10 +1831,10 @@
         <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C89">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
@@ -1842,10 +1842,10 @@
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
@@ -1853,10 +1853,10 @@
         <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C91">
-        <v>46</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
@@ -1864,10 +1864,10 @@
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C92">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
@@ -1875,10 +1875,10 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C93">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
@@ -1886,32 +1886,32 @@
         <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>5</v>
       </c>
-      <c r="B95" s="3">
-        <v>46327</v>
+      <c r="B95" t="s">
+        <v>33</v>
       </c>
       <c r="C95">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="B96" s="3">
+        <v>46327</v>
       </c>
       <c r="C96">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -1919,10 +1919,10 @@
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C97">
-        <v>61</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
@@ -1930,10 +1930,10 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C98">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
@@ -1941,10 +1941,10 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C99">
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
@@ -1952,32 +1952,32 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>6</v>
       </c>
-      <c r="B101" s="3">
-        <v>46357</v>
+      <c r="B101" t="s">
+        <v>36</v>
       </c>
       <c r="C101">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>24</v>
-      </c>
-      <c r="B102" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="B102" s="3">
+        <v>46357</v>
       </c>
       <c r="C102">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
@@ -1985,10 +1985,10 @@
         <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C103">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
@@ -1996,10 +1996,10 @@
         <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C104">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
@@ -2007,10 +2007,10 @@
         <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C105">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
@@ -2018,21 +2018,21 @@
         <v>24</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C106">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C107">
-        <v>196</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
@@ -2040,10 +2040,10 @@
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C108">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
@@ -2051,10 +2051,10 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C109">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
@@ -2062,10 +2062,10 @@
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C110">
-        <v>266</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
@@ -2073,10 +2073,10 @@
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C111">
-        <v>56</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
@@ -2084,10 +2084,10 @@
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C112">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
@@ -2095,10 +2095,10 @@
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C113">
-        <v>161</v>
+        <v>68</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
@@ -2106,10 +2106,10 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C114">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
@@ -2117,10 +2117,10 @@
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C115">
-        <v>72</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
@@ -2128,10 +2128,10 @@
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
@@ -2139,10 +2139,10 @@
         <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C117">
-        <v>155</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
@@ -2150,21 +2150,21 @@
         <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>22</v>
       </c>
-      <c r="B119" s="3">
-        <v>46327</v>
+      <c r="B119" t="s">
+        <v>33</v>
       </c>
       <c r="C119">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
@@ -2172,7 +2172,7 @@
         <v>22</v>
       </c>
       <c r="B120" s="3">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="C120">
         <v>70</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>7</v>
-      </c>
-      <c r="B121" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="B121" s="3">
+        <v>46357</v>
       </c>
       <c r="C121">
-        <v>650</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
@@ -2194,10 +2194,10 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C122">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
@@ -2205,10 +2205,10 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C123">
-        <v>821</v>
+        <v>670</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
@@ -2216,10 +2216,10 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C124">
-        <v>919</v>
+        <v>821</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
@@ -2227,10 +2227,10 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C125">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
@@ -2238,10 +2238,10 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>1052</v>
+        <v>918</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
@@ -2249,10 +2249,10 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C127">
-        <v>502</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
@@ -2260,10 +2260,10 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C128">
-        <v>375</v>
+        <v>502</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
@@ -2271,10 +2271,10 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C129">
-        <v>560</v>
+        <v>375</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
@@ -2282,10 +2282,10 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C130">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
@@ -2293,10 +2293,10 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C131">
-        <v>695</v>
+        <v>565</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -2304,21 +2304,21 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C132">
-        <v>290</v>
+        <v>695</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>7</v>
       </c>
-      <c r="B133" s="3">
-        <v>46327</v>
+      <c r="B133" t="s">
+        <v>33</v>
       </c>
       <c r="C133">
-        <v>263</v>
+        <v>290</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
@@ -2326,21 +2326,21 @@
         <v>7</v>
       </c>
       <c r="B134" s="3">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="C134">
-        <v>288</v>
+        <v>263</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>8</v>
-      </c>
-      <c r="B135" t="s">
-        <v>31</v>
+        <v>7</v>
+      </c>
+      <c r="B135" s="3">
+        <v>46357</v>
       </c>
       <c r="C135">
-        <v>20</v>
+        <v>288</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
@@ -2348,10 +2348,10 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C136">
-        <v>420</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
@@ -2359,10 +2359,10 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C137">
-        <v>725</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
@@ -2370,10 +2370,10 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C138">
-        <v>190</v>
+        <v>725</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
@@ -2381,10 +2381,10 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C139">
-        <v>474</v>
+        <v>190</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
@@ -2392,10 +2392,10 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C140">
-        <v>65</v>
+        <v>474</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
@@ -2403,21 +2403,21 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C141">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>8</v>
       </c>
-      <c r="B142" s="3">
-        <v>46327</v>
+      <c r="B142" t="s">
+        <v>33</v>
       </c>
       <c r="C142">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
@@ -2425,21 +2425,21 @@
         <v>8</v>
       </c>
       <c r="B143" s="3">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="C143">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="B144" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="B144" s="3">
+        <v>46357</v>
       </c>
       <c r="C144">
-        <v>6</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
@@ -2447,10 +2447,10 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C145">
-        <v>485</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
@@ -2458,10 +2458,10 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C146">
-        <v>215</v>
+        <v>485</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -2469,10 +2469,10 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C147">
-        <v>100</v>
+        <v>215</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
@@ -2480,10 +2480,10 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C148">
-        <v>772</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
@@ -2491,10 +2491,10 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C149">
-        <v>236</v>
+        <v>772</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
@@ -2502,10 +2502,10 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>236</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
@@ -2513,10 +2513,10 @@
         <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C151">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
@@ -2524,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="B152" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152">
         <v>35</v>
-      </c>
-      <c r="C152">
-        <v>350</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -2535,10 +2535,10 @@
         <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C153">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
@@ -2546,21 +2546,21 @@
         <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>9</v>
       </c>
-      <c r="B155" s="3">
-        <v>46327</v>
+      <c r="B155" t="s">
+        <v>33</v>
       </c>
       <c r="C155">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
@@ -2568,21 +2568,21 @@
         <v>9</v>
       </c>
       <c r="B156" s="3">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="C156">
-        <v>185</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>10</v>
-      </c>
-      <c r="B157" t="s">
-        <v>41</v>
+        <v>9</v>
+      </c>
+      <c r="B157" s="3">
+        <v>46357</v>
       </c>
       <c r="C157">
-        <v>500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
@@ -2590,10 +2590,10 @@
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C158">
-        <v>61</v>
+        <v>500</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
@@ -2601,10 +2601,10 @@
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C159">
-        <v>434</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
@@ -2612,20 +2612,31 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>434</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>10</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B161" t="s">
+        <v>36</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162" s="3">
         <v>46327</v>
       </c>
-      <c r="C161">
+      <c r="C162">
         <v>50</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="67">
   <si>
     <t>시트구분</t>
   </si>
@@ -3657,7 +3657,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
@@ -3838,29 +3838,15 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46290</v>
+        <v>65</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46296</v>
       </c>
       <c r="C15">
         <v>3000</v>
       </c>
       <c r="D15">
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="4">
-        <v>46296</v>
-      </c>
-      <c r="C16">
-        <v>3000</v>
-      </c>
-      <c r="D16">
         <v>44.5</v>
       </c>
     </row>
